--- a/output/pdf_financials_xlsx/SRAN.xlsx
+++ b/output/pdf_financials_xlsx/SRAN.xlsx
@@ -1934,13 +1934,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.084839</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.084839</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>3.033286</v>
       </c>
     </row>
     <row r="93">
@@ -3101,7 +3101,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -3324,7 +3328,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" s="5" t="n">
         <v>0.084839</v>
       </c>

--- a/output/pdf_financials_xlsx/SRAN.xlsx
+++ b/output/pdf_financials_xlsx/SRAN.xlsx
@@ -615,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.06661499999999999</v>
       </c>
     </row>
     <row r="13">
@@ -885,7 +885,7 @@
         <v>-0.029929</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-3.830536</v>
+        <v>-3.897151</v>
       </c>
     </row>
     <row r="28">
@@ -917,7 +917,7 @@
         <v>-0.029929</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.830536</v>
+        <v>-3.897151</v>
       </c>
     </row>
     <row r="30">
@@ -994,13 +994,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.015248</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.004899</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>5.678489</v>
       </c>
     </row>
     <row r="35">
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.015248</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.004899</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>5.678489</v>
       </c>
     </row>
     <row r="37">
@@ -1218,13 +1218,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.022946</v>
+        <v>0.007698</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.005549</v>
+        <v>0.00065</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>5.841317</v>
+        <v>0.162828</v>
       </c>
     </row>
     <row r="49">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">

--- a/output/pdf_financials_xlsx/SRAN.xlsx
+++ b/output/pdf_financials_xlsx/SRAN.xlsx
@@ -1528,13 +1528,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.0182</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.106953</v>
       </c>
     </row>
     <row r="68">
@@ -2235,7 +2235,7 @@
         <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.541577</v>
       </c>
     </row>
     <row r="112">
@@ -2625,7 +2625,7 @@
         <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.541577</v>
       </c>
     </row>
     <row r="135">
@@ -2641,7 +2641,7 @@
         <v>-0.010349</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-1.030003</v>
+        <v>-1.57158</v>
       </c>
     </row>
   </sheetData>
@@ -3553,7 +3553,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
